--- a/Result/profitability/5209.xlsx
+++ b/Result/profitability/5209.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.64</v>
       </c>
       <c r="M2" t="n">
-        <v>3.26375</v>
+        <v>3.465</v>
       </c>
       <c r="N2" t="n">
-        <v>13.06625</v>
+        <v>14.44375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>2.825</v>
+        <v>3.22125</v>
       </c>
       <c r="N3" t="n">
-        <v>14.52375</v>
+        <v>16.055</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.55</v>
       </c>
       <c r="M4" t="n">
-        <v>2.61875</v>
+        <v>3.09375</v>
       </c>
       <c r="N4" t="n">
-        <v>15.8125</v>
+        <v>17.3925</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.14</v>
       </c>
       <c r="M5" t="n">
-        <v>2.44</v>
+        <v>2.48125</v>
       </c>
       <c r="N5" t="n">
-        <v>15.605</v>
+        <v>15.91875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.47</v>
       </c>
       <c r="M6" t="n">
-        <v>1.86875</v>
+        <v>1.8225</v>
       </c>
       <c r="N6" t="n">
-        <v>15.7575</v>
+        <v>16.41</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>0.41</v>
       </c>
       <c r="M7" t="n">
-        <v>1.2025</v>
+        <v>1.39625</v>
       </c>
       <c r="N7" t="n">
-        <v>15.615</v>
+        <v>16.93375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7949999999999999</v>
+        <v>1.04875</v>
       </c>
       <c r="N8" t="n">
-        <v>15.96625</v>
+        <v>16.27125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5209</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>931</v>
+      </c>
+      <c r="D75" t="n">
+        <v>740</v>
+      </c>
+      <c r="E75" t="n">
+        <v>190</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.44</v>
+      </c>
+      <c r="G75" t="n">
+        <v>147</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.80%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>36</v>
+      </c>
+      <c r="J75" t="n">
+        <v>183</v>
+      </c>
+      <c r="K75" t="n">
+        <v>153</v>
+      </c>
+      <c r="L75" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.855</v>
+      </c>
+      <c r="N75" t="n">
+        <v>13.36125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6077844311377247</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.440000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1355555555555557</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.3300000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.06547619047619047</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.510000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.139988845510318</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
